--- a/Excel/MapDataConfig.xlsx
+++ b/Excel/MapDataConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Datas\UnityProject\NodeGraphProcessor-master\NodeGraphProcessor-odin\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Datas\UnityProject\CardRougelike\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A947E84-6FF4-4C85-A4FE-CB6AF9C806BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487AFFCD-B93F-4DC4-BFFC-26A437AD75CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="3060" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="3330" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapData" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +71,22 @@
   </si>
   <si>
     <t>测试关卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -393,70 +412,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="13.08203125" customWidth="1"/>
+    <col min="5" max="5" width="13.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
+      <c r="E5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>